--- a/research/traditional_assets/database/data/kuwait/kuwait_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/kuwait/kuwait_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ13"/>
+  <dimension ref="A1:AQ12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.005180000000000001</v>
+        <v>0.0439</v>
       </c>
       <c r="E2">
-        <v>-0.034</v>
+        <v>0.0745</v>
       </c>
       <c r="F2">
-        <v>0.201</v>
+        <v>0.189</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,91 +603,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.0005712944739727756</v>
+        <v>0.0005016591089305767</v>
       </c>
       <c r="J2">
-        <v>0.0005360556503708698</v>
+        <v>0.0004313894322071127</v>
       </c>
       <c r="K2">
-        <v>2413.5</v>
+        <v>3311.7</v>
       </c>
       <c r="L2">
-        <v>0.2950561138414142</v>
+        <v>0.3468620386275085</v>
       </c>
       <c r="M2">
-        <v>2005.127</v>
+        <v>2244.987</v>
       </c>
       <c r="N2">
-        <v>0.02821336961675866</v>
+        <v>0.02655648520221491</v>
       </c>
       <c r="O2">
-        <v>0.8307963538429666</v>
+        <v>0.677895642721261</v>
       </c>
       <c r="P2">
-        <v>1016.5</v>
+        <v>1843.5</v>
       </c>
       <c r="Q2">
-        <v>0.01430277993136354</v>
+        <v>0.02180719998391224</v>
       </c>
       <c r="R2">
-        <v>0.4211725709550446</v>
+        <v>0.5566627411903252</v>
       </c>
       <c r="S2">
-        <v>988.6270000000001</v>
+        <v>401.487</v>
       </c>
       <c r="T2">
-        <v>0.4930495674338833</v>
+        <v>0.1788371157605812</v>
       </c>
       <c r="U2">
-        <v>45480.5</v>
+        <v>32876.2</v>
       </c>
       <c r="V2">
-        <v>0.6399385958370678</v>
+        <v>0.3889003895368025</v>
       </c>
       <c r="W2">
-        <v>0.06208360065143365</v>
+        <v>0.06098694676515504</v>
       </c>
       <c r="X2">
-        <v>0.06935582055157073</v>
+        <v>0.0944958016652722</v>
       </c>
       <c r="Y2">
-        <v>-0.007272219900137086</v>
+        <v>-0.03350885490011717</v>
       </c>
       <c r="Z2">
-        <v>0.1520755625176854</v>
+        <v>0.1649889957237101</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04637934173678009</v>
+        <v>0.07332101501507307</v>
       </c>
       <c r="AC2">
-        <v>-0.04637934173678009</v>
+        <v>-0.07332101501507307</v>
       </c>
       <c r="AD2">
-        <v>64696.4</v>
+        <v>56132.4</v>
       </c>
       <c r="AE2">
-        <v>10.63462730898745</v>
+        <v>9.001797457872131</v>
       </c>
       <c r="AF2">
-        <v>64707.03462730899</v>
+        <v>56141.40179745787</v>
       </c>
       <c r="AG2">
-        <v>19226.53462730899</v>
+        <v>23265.20179745788</v>
       </c>
       <c r="AH2">
-        <v>0.4765679788789297</v>
+        <v>0.3990781842476217</v>
       </c>
       <c r="AI2">
-        <v>0.6078669712108163</v>
+        <v>0.581163693318447</v>
       </c>
       <c r="AJ2">
-        <v>0.2129263699213679</v>
+        <v>0.2158151918993628</v>
       </c>
       <c r="AK2">
-        <v>0.3153502071154414</v>
+        <v>0.3650846386647985</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>9514.176470588236</v>
+        <v>8517.814871016692</v>
       </c>
       <c r="AP2">
-        <v>2827.431562839558</v>
+        <v>3530.379635426082</v>
       </c>
     </row>
     <row r="3">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.00116</v>
+        <v>-0.00993</v>
       </c>
       <c r="E3">
-        <v>-0.047</v>
+        <v>-0.035</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -737,61 +737,61 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>111.7</v>
+        <v>111.3</v>
       </c>
       <c r="L3">
-        <v>0.4854411125597566</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="M3">
-        <v>50.8</v>
+        <v>218</v>
       </c>
       <c r="N3">
-        <v>0.02318364366557138</v>
+        <v>0.1045112421496716</v>
       </c>
       <c r="O3">
-        <v>0.4547896150402864</v>
+        <v>1.958670260557053</v>
       </c>
       <c r="P3">
-        <v>11.4</v>
+        <v>61.7</v>
       </c>
       <c r="Q3">
-        <v>0.005202628696604601</v>
+        <v>0.02957955798456302</v>
       </c>
       <c r="R3">
-        <v>0.1020590868397493</v>
+        <v>0.5543575920934412</v>
       </c>
       <c r="S3">
-        <v>39.4</v>
+        <v>156.3</v>
       </c>
       <c r="T3">
-        <v>0.7755905511811024</v>
+        <v>0.7169724770642202</v>
       </c>
       <c r="U3">
-        <v>536</v>
+        <v>591.2</v>
       </c>
       <c r="V3">
-        <v>0.244614822928076</v>
+        <v>0.2834268181600268</v>
       </c>
       <c r="W3">
-        <v>0.06890383073221887</v>
+        <v>0.04818181818181818</v>
       </c>
       <c r="X3">
-        <v>0.04285199133200564</v>
+        <v>0.07041257893186294</v>
       </c>
       <c r="Y3">
-        <v>0.02605183940021323</v>
+        <v>-0.02223076075004476</v>
       </c>
       <c r="Z3">
-        <v>0.2151673835795773</v>
+        <v>0.1344419391206313</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.04285199133200564</v>
+        <v>0.07041257893186294</v>
       </c>
       <c r="AC3">
-        <v>-0.04285199133200564</v>
+        <v>-0.07041257893186294</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -803,7 +803,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-536</v>
+        <v>-591.2</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -812,10 +812,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.3238279362010634</v>
+        <v>-0.3955308757610223</v>
       </c>
       <c r="AK3">
-        <v>-0.3021420518602029</v>
+        <v>-0.3820602300633321</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -832,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Gulf Bank K.S.C.P. (KWSE:GBK)</t>
+          <t>Kuwait Finance House K.S.C.P. (KWSE:KFH)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -841,13 +841,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.005180000000000001</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="E4">
-        <v>-0.021</v>
-      </c>
-      <c r="F4">
-        <v>0.291</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -862,85 +859,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>125.8</v>
+        <v>905.7</v>
       </c>
       <c r="L4">
-        <v>0.3271781534460338</v>
+        <v>0.3332842686292549</v>
       </c>
       <c r="M4">
-        <v>49.9</v>
+        <v>360.987</v>
       </c>
       <c r="N4">
-        <v>0.0179670903395384</v>
+        <v>0.01009203371587526</v>
       </c>
       <c r="O4">
-        <v>0.3966613672496025</v>
+        <v>0.3985723749585955</v>
       </c>
       <c r="P4">
-        <v>49.9</v>
+        <v>360.7</v>
       </c>
       <c r="Q4">
-        <v>0.0179670903395384</v>
+        <v>0.01008401012035393</v>
       </c>
       <c r="R4">
-        <v>0.3966613672496025</v>
+        <v>0.3982554929888484</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>0.2869999999999777</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.0007950424807540929</v>
       </c>
       <c r="U4">
-        <v>2906.3</v>
+        <v>7257.5</v>
       </c>
       <c r="V4">
-        <v>1.046447989054117</v>
+        <v>0.2028963222857463</v>
       </c>
       <c r="W4">
-        <v>0.06208360065143365</v>
+        <v>0.1267422334172964</v>
       </c>
       <c r="X4">
-        <v>0.04707669317021493</v>
+        <v>0.07873194262366122</v>
       </c>
       <c r="Y4">
-        <v>0.01500690748121872</v>
+        <v>0.04801029079363518</v>
       </c>
       <c r="Z4">
-        <v>-1.134218289085546</v>
+        <v>0.4155643570412735</v>
       </c>
       <c r="AA4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.04445619320022115</v>
+        <v>0.07135758704624885</v>
       </c>
       <c r="AC4">
-        <v>-0.04445619320022115</v>
+        <v>-0.07135758704624885</v>
       </c>
       <c r="AD4">
-        <v>497.4</v>
+        <v>11074.5</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>497.4</v>
+        <v>11074.5</v>
       </c>
       <c r="AG4">
-        <v>-2408.9</v>
+        <v>3817</v>
       </c>
       <c r="AH4">
-        <v>0.1518917763459248</v>
+        <v>0.2364123473657245</v>
       </c>
       <c r="AI4">
-        <v>0.1866626637144894</v>
+        <v>0.5826139107652973</v>
       </c>
       <c r="AJ4">
-        <v>-6.538816503800216</v>
+        <v>0.09642175994341505</v>
       </c>
       <c r="AK4">
-        <v>9.970612582781461</v>
+        <v>0.3248289478163189</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -957,7 +954,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kuwait Finance House K.S.C.P. (KWSE:KFH)</t>
+          <t>Warba Bank K.S.C.P. (KWSE:WARBABANK)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -966,13 +963,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0219</v>
+        <v>0.197</v>
       </c>
       <c r="E5">
-        <v>0.05690000000000001</v>
-      </c>
-      <c r="F5">
-        <v>0.32</v>
+        <v>0.276</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -987,85 +981,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>713.8</v>
+        <v>72.2</v>
       </c>
       <c r="L5">
-        <v>0.3396621460861289</v>
+        <v>0.386509635974304</v>
       </c>
       <c r="M5">
-        <v>239.4</v>
+        <v>257.3</v>
       </c>
       <c r="N5">
-        <v>0.01039057990199695</v>
+        <v>0.1678736869576564</v>
       </c>
       <c r="O5">
-        <v>0.3353880638834408</v>
+        <v>3.563711911357341</v>
       </c>
       <c r="P5">
-        <v>239.4</v>
+        <v>12.4</v>
       </c>
       <c r="Q5">
-        <v>0.01039057990199695</v>
+        <v>0.008090298166634044</v>
       </c>
       <c r="R5">
-        <v>0.3353880638834408</v>
+        <v>0.1717451523545706</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>244.9</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>0.9518072289156626</v>
       </c>
       <c r="U5">
-        <v>10021.6</v>
+        <v>1351.8</v>
       </c>
       <c r="V5">
-        <v>0.4349633899158424</v>
+        <v>0.8819729888432178</v>
       </c>
       <c r="W5">
-        <v>0.1170586113024369</v>
+        <v>0.07925356750823272</v>
       </c>
       <c r="X5">
-        <v>0.05249126762477108</v>
+        <v>0.08770926113845887</v>
       </c>
       <c r="Y5">
-        <v>0.06456734367766585</v>
+        <v>-0.008455693630226149</v>
       </c>
       <c r="Z5">
-        <v>0.2757078008973787</v>
+        <v>0.2799760191846523</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.04449700257654836</v>
+        <v>0.07197798353632466</v>
       </c>
       <c r="AC5">
-        <v>-0.04449700257654836</v>
+        <v>-0.07197798353632466</v>
       </c>
       <c r="AD5">
-        <v>9414.9</v>
+        <v>986.6</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>9414.9</v>
+        <v>986.6</v>
       </c>
       <c r="AG5">
-        <v>-606.7000000000007</v>
+        <v>-365.1999999999999</v>
       </c>
       <c r="AH5">
-        <v>0.290090895085503</v>
+        <v>0.3916167189298614</v>
       </c>
       <c r="AI5">
-        <v>0.5501092634358968</v>
+        <v>0.4563578333872982</v>
       </c>
       <c r="AJ5">
-        <v>-0.02704449615305753</v>
+        <v>-0.3128051391862954</v>
       </c>
       <c r="AK5">
-        <v>-0.08553503454109697</v>
+        <v>-0.4508085421552894</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1082,7 +1076,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Warba Bank K.S.C.P. (KWSE:WARBABANK)</t>
+          <t>Boubyan Bank K.S.C.P. (KWSE:BOUBYAN)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1091,10 +1085,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.27</v>
+        <v>0.105</v>
       </c>
       <c r="E6">
-        <v>1.111</v>
+        <v>0.0745</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1109,28 +1103,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>87.09999999999999</v>
+        <v>210.1</v>
       </c>
       <c r="L6">
-        <v>0.4904279279279279</v>
+        <v>0.4034178187403994</v>
       </c>
       <c r="M6">
-        <v>16.3</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="N6">
-        <v>0.008997571207772136</v>
+        <v>0.008264802631578949</v>
       </c>
       <c r="O6">
-        <v>0.1871412169919633</v>
+        <v>0.3826749167063304</v>
       </c>
       <c r="P6">
-        <v>16.3</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="Q6">
-        <v>0.008997571207772136</v>
+        <v>0.008264802631578949</v>
       </c>
       <c r="R6">
-        <v>0.1871412169919633</v>
+        <v>0.3826749167063304</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1139,55 +1133,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>1348.6</v>
+        <v>2202.3</v>
       </c>
       <c r="V6">
-        <v>0.7444248178405829</v>
+        <v>0.2263877467105263</v>
       </c>
       <c r="W6">
-        <v>0.1023261278195489</v>
+        <v>0.09031509263637535</v>
       </c>
       <c r="X6">
-        <v>0.05586667340083357</v>
+        <v>0.07815530477513177</v>
       </c>
       <c r="Y6">
-        <v>0.04645945441871529</v>
+        <v>0.01215978786124358</v>
       </c>
       <c r="Z6">
-        <v>0.5488257107540174</v>
+        <v>0.2096196417790299</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.0448682269203954</v>
+        <v>0.07239052308785689</v>
       </c>
       <c r="AC6">
-        <v>-0.0448682269203954</v>
+        <v>-0.07239052308785689</v>
       </c>
       <c r="AD6">
-        <v>999.5</v>
+        <v>2803.1</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>999.5</v>
+        <v>2803.1</v>
       </c>
       <c r="AG6">
-        <v>-349.0999999999999</v>
+        <v>600.7999999999997</v>
       </c>
       <c r="AH6">
-        <v>0.355554765038597</v>
+        <v>0.2236914556583221</v>
       </c>
       <c r="AI6">
-        <v>0.5196797171528102</v>
+        <v>0.4722362613295596</v>
       </c>
       <c r="AJ6">
-        <v>-0.2387008547008546</v>
+        <v>0.05816745410889937</v>
       </c>
       <c r="AK6">
-        <v>-0.6074473638420044</v>
+        <v>0.1609213874380608</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1204,7 +1198,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Boubyan Bank K.S.C.P. (KWSE:BOUBYAN)</t>
+          <t>Al Ahli Bank of Kuwait K.S.C.P. (KWSE:ABK)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1213,13 +1207,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0935</v>
+        <v>0.0545</v>
       </c>
       <c r="E7">
-        <v>0.0164</v>
-      </c>
-      <c r="F7">
-        <v>0.148</v>
+        <v>-0.00646</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1234,85 +1225,85 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>142.8</v>
+        <v>108.4</v>
       </c>
       <c r="L7">
-        <v>0.3318614919823379</v>
+        <v>0.2695846804277543</v>
       </c>
       <c r="M7">
-        <v>266.4</v>
+        <v>48.8</v>
       </c>
       <c r="N7">
-        <v>0.03208401580113691</v>
+        <v>0.02608649168760357</v>
       </c>
       <c r="O7">
-        <v>1.865546218487395</v>
+        <v>0.4501845018450184</v>
       </c>
       <c r="P7">
-        <v>16.4</v>
+        <v>48.8</v>
       </c>
       <c r="Q7">
-        <v>0.001975142113883803</v>
+        <v>0.02608649168760357</v>
       </c>
       <c r="R7">
-        <v>0.1148459383753501</v>
+        <v>0.4501845018450184</v>
       </c>
       <c r="S7">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>0.9384384384384384</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>3165.6</v>
+        <v>1473.1</v>
       </c>
       <c r="V7">
-        <v>0.3812506021774737</v>
+        <v>0.787459239856738</v>
       </c>
       <c r="W7">
-        <v>0.07541191381495566</v>
+        <v>0.05453264915987524</v>
       </c>
       <c r="X7">
-        <v>0.05229482764462273</v>
+        <v>0.1202742528823892</v>
       </c>
       <c r="Y7">
-        <v>0.02311708617033292</v>
+        <v>-0.06574160372251393</v>
       </c>
       <c r="Z7">
-        <v>0.1546562196743701</v>
+        <v>0.1252179870453413</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.04559514112252611</v>
+        <v>0.07301006751330517</v>
       </c>
       <c r="AC7">
-        <v>-0.04559514112252611</v>
+        <v>-0.07301006751330517</v>
       </c>
       <c r="AD7">
-        <v>3323.8</v>
+        <v>3471.3</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>3323.8</v>
+        <v>3471.3</v>
       </c>
       <c r="AG7">
-        <v>158.2000000000003</v>
+        <v>1998.2</v>
       </c>
       <c r="AH7">
-        <v>0.2858690977896276</v>
+        <v>0.6498128041931861</v>
       </c>
       <c r="AI7">
-        <v>0.576648160999306</v>
+        <v>0.6422030229589477</v>
       </c>
       <c r="AJ7">
-        <v>0.01869666958186592</v>
+        <v>0.5164775517588979</v>
       </c>
       <c r="AK7">
-        <v>0.06088362068965528</v>
+        <v>0.5081633691063527</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1329,7 +1320,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Al Ahli Bank of Kuwait K.S.C.P. (KWSE:ABK)</t>
+          <t>Kuwait International Bank K.S.C.P. (KWSE:KIB)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1338,7 +1329,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>-0.115</v>
+        <v>0.0108</v>
+      </c>
+      <c r="E8">
+        <v>-0.0949</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1353,28 +1347,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>-134.9</v>
+        <v>35.6</v>
       </c>
       <c r="L8">
-        <v>-1.028201219512195</v>
+        <v>0.1993281075027996</v>
       </c>
       <c r="M8">
-        <v>21.9</v>
+        <v>29.8</v>
       </c>
       <c r="N8">
-        <v>0.01546719401087647</v>
+        <v>0.04396577161404545</v>
       </c>
       <c r="O8">
-        <v>-0.16234247590808</v>
+        <v>0.8370786516853932</v>
       </c>
       <c r="P8">
-        <v>21.9</v>
+        <v>29.8</v>
       </c>
       <c r="Q8">
-        <v>0.01546719401087647</v>
+        <v>0.04396577161404545</v>
       </c>
       <c r="R8">
-        <v>-0.16234247590808</v>
+        <v>0.8370786516853932</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1383,55 +1377,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>1887.1</v>
+        <v>443.1</v>
       </c>
       <c r="V8">
-        <v>1.332791863832191</v>
+        <v>0.6537326645028033</v>
       </c>
       <c r="W8">
-        <v>-0.06372826908541195</v>
+        <v>0.03058944835882454</v>
       </c>
       <c r="X8">
-        <v>0.0816736148022815</v>
+        <v>0.1816179173613457</v>
       </c>
       <c r="Y8">
-        <v>-0.1454018838876934</v>
+        <v>-0.1510284690025211</v>
       </c>
       <c r="Z8">
-        <v>0.03025620921061734</v>
+        <v>0.08220565221393722</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.04637934173678009</v>
+        <v>0.07363196251684097</v>
       </c>
       <c r="AC8">
-        <v>-0.04637934173678009</v>
+        <v>-0.07363196251684097</v>
       </c>
       <c r="AD8">
-        <v>2330.2</v>
+        <v>2805.1</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>2330.2</v>
+        <v>2805.1</v>
       </c>
       <c r="AG8">
-        <v>443.0999999999999</v>
+        <v>2362</v>
       </c>
       <c r="AH8">
-        <v>0.6220335815915218</v>
+        <v>0.8053920583421862</v>
       </c>
       <c r="AI8">
-        <v>0.5378543070815253</v>
+        <v>0.7204386685843436</v>
       </c>
       <c r="AJ8">
-        <v>0.2383539537385691</v>
+        <v>0.7770248042634383</v>
       </c>
       <c r="AK8">
-        <v>0.1812047601521285</v>
+        <v>0.6845384726851181</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1448,7 +1442,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kuwait International Bank K.S.C.P. (KWSE:KIB)</t>
+          <t>National Bank of Kuwait S.A.K.P. (KWSE:NBK)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1457,10 +1451,13 @@
         </is>
       </c>
       <c r="D9">
-        <v>-0.0269</v>
+        <v>0.0824</v>
       </c>
       <c r="E9">
-        <v>-0.289</v>
+        <v>0.0892</v>
+      </c>
+      <c r="F9">
+        <v>0.189</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1475,28 +1472,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>10.7</v>
+        <v>1552</v>
       </c>
       <c r="L9">
-        <v>0.07572540693559801</v>
+        <v>0.518976759739174</v>
       </c>
       <c r="M9">
-        <v>17.7</v>
+        <v>1002.7</v>
       </c>
       <c r="N9">
-        <v>0.02408818726183996</v>
+        <v>0.0377671895892578</v>
       </c>
       <c r="O9">
-        <v>1.654205607476636</v>
+        <v>0.646069587628866</v>
       </c>
       <c r="P9">
-        <v>17.7</v>
+        <v>1002.7</v>
       </c>
       <c r="Q9">
-        <v>0.02408818726183996</v>
+        <v>0.0377671895892578</v>
       </c>
       <c r="R9">
-        <v>1.654205607476636</v>
+        <v>0.646069587628866</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1505,55 +1502,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>871.6</v>
+        <v>12328.9</v>
       </c>
       <c r="V9">
-        <v>1.186173108328797</v>
+        <v>0.4643740936740805</v>
       </c>
       <c r="W9">
-        <v>0.009311635192759552</v>
+        <v>0.1206739703446828</v>
       </c>
       <c r="X9">
-        <v>0.1032182376923729</v>
+        <v>0.08612215947066411</v>
       </c>
       <c r="Y9">
-        <v>-0.09390660249961337</v>
+        <v>0.03455181087401869</v>
       </c>
       <c r="Z9">
-        <v>0.0584488107549121</v>
+        <v>0.1223518726116734</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.04692936118758471</v>
+        <v>0.07367485553575144</v>
       </c>
       <c r="AC9">
-        <v>-0.04692936118758471</v>
+        <v>-0.07367485553575144</v>
       </c>
       <c r="AD9">
-        <v>1880.4</v>
+        <v>15521.8</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>1880.4</v>
+        <v>15521.8</v>
       </c>
       <c r="AG9">
-        <v>1008.8</v>
+        <v>3192.9</v>
       </c>
       <c r="AH9">
-        <v>0.7190272254512085</v>
+        <v>0.3689403465070012</v>
       </c>
       <c r="AI9">
-        <v>0.6152537381801525</v>
+        <v>0.5170796383527327</v>
       </c>
       <c r="AJ9">
-        <v>0.5785730672172518</v>
+        <v>0.1073517940717629</v>
       </c>
       <c r="AK9">
-        <v>0.4617567629422804</v>
+        <v>0.1804989456903326</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1570,7 +1567,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>National Bank of Kuwait S.A.K.P. (KWSE:NBK)</t>
+          <t>Commercial Bank of Kuwait K.P.S.C. (KWSE:CBK)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1579,13 +1576,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.0429</v>
+        <v>0.0333</v>
       </c>
       <c r="E10">
-        <v>0.0398</v>
-      </c>
-      <c r="F10">
-        <v>0.201</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1600,85 +1594,85 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>1102.4</v>
+        <v>178.2</v>
       </c>
       <c r="L10">
-        <v>0.4732345996995064</v>
+        <v>0.5198366394399067</v>
       </c>
       <c r="M10">
-        <v>1239.4</v>
+        <v>127.7</v>
       </c>
       <c r="N10">
-        <v>0.05227991732399714</v>
+        <v>0.04139652489626556</v>
       </c>
       <c r="O10">
-        <v>1.124274310595065</v>
+        <v>0.7166105499438833</v>
       </c>
       <c r="P10">
-        <v>540.8</v>
+        <v>127.7</v>
       </c>
       <c r="Q10">
-        <v>0.02281182773020627</v>
+        <v>0.04139652489626556</v>
       </c>
       <c r="R10">
-        <v>0.4905660377358489</v>
+        <v>0.7166105499438833</v>
       </c>
       <c r="S10">
-        <v>698.6000000000001</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>0.5636598354042279</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>17294</v>
+        <v>1605.5</v>
       </c>
       <c r="V10">
-        <v>0.7294891804108491</v>
+        <v>0.5204551348547718</v>
       </c>
       <c r="W10">
-        <v>0.09379254015790907</v>
+        <v>0.06744124437043483</v>
       </c>
       <c r="X10">
-        <v>0.07158320407495597</v>
+        <v>0.1012823421920855</v>
       </c>
       <c r="Y10">
-        <v>0.0222093360829531</v>
+        <v>-0.03384109782165071</v>
       </c>
       <c r="Z10">
-        <v>0.1123506091385248</v>
+        <v>0.07486350731600785</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.04742861489067661</v>
+        <v>0.0777756530749894</v>
       </c>
       <c r="AC10">
-        <v>-0.04742861489067661</v>
+        <v>-0.0777756530749894</v>
       </c>
       <c r="AD10">
-        <v>28874.7</v>
+        <v>3543.9</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>28874.7</v>
+        <v>3543.9</v>
       </c>
       <c r="AG10">
-        <v>11580.7</v>
+        <v>1938.4</v>
       </c>
       <c r="AH10">
-        <v>0.5491397197123714</v>
+        <v>0.5346297162339523</v>
       </c>
       <c r="AI10">
-        <v>0.6663335925619092</v>
+        <v>0.6208110712095998</v>
       </c>
       <c r="AJ10">
-        <v>0.3281795073070787</v>
+        <v>0.3858894728459946</v>
       </c>
       <c r="AK10">
-        <v>0.4447324661958471</v>
+        <v>0.4724348038020961</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1695,7 +1689,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Commercial Bank of Kuwait K.P.S.C. (KWSE:CBK)</t>
+          <t>Burgan Bank K.P.S.C. (KWSE:BURG)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1704,10 +1698,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>-0.0616</v>
+        <v>-0.0154</v>
       </c>
       <c r="E11">
-        <v>-0.133</v>
+        <v>-0.08800000000000001</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1722,82 +1716,85 @@
         <v>0</v>
       </c>
       <c r="K11">
+        <v>149.4</v>
+      </c>
+      <c r="L11">
+        <v>0.2529630883846936</v>
+      </c>
+      <c r="M11">
         <v>78.59999999999999</v>
       </c>
-      <c r="L11">
-        <v>0.3681498829039813</v>
-      </c>
-      <c r="M11">
-        <v>-0</v>
-      </c>
       <c r="N11">
-        <v>-0</v>
+        <v>0.03352670192799863</v>
       </c>
       <c r="O11">
-        <v>-0</v>
+        <v>0.5261044176706827</v>
       </c>
       <c r="P11">
-        <v>-0</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="Q11">
-        <v>-0</v>
+        <v>0.03352670192799863</v>
       </c>
       <c r="R11">
-        <v>-0</v>
+        <v>0.5261044176706827</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
       <c r="U11">
-        <v>1745.2</v>
+        <v>1872.6</v>
       </c>
       <c r="V11">
-        <v>0.5325602685382972</v>
+        <v>0.7987544787578911</v>
       </c>
       <c r="W11">
-        <v>0.03386909122247598</v>
+        <v>0.05365801099019502</v>
       </c>
       <c r="X11">
-        <v>0.06935582055157073</v>
+        <v>0.1312269472868304</v>
       </c>
       <c r="Y11">
-        <v>-0.03548672932909475</v>
+        <v>-0.07756893629663542</v>
       </c>
       <c r="Z11">
-        <v>0.04555832959904402</v>
+        <v>0.1162072290104874</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.04929926534164296</v>
+        <v>0.07884432037971015</v>
       </c>
       <c r="AC11">
-        <v>-0.04929926534164296</v>
+        <v>-0.07884432037971015</v>
       </c>
       <c r="AD11">
-        <v>3681.9</v>
+        <v>5305.9</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>3681.9</v>
+        <v>5305.9</v>
       </c>
       <c r="AG11">
-        <v>1936.7</v>
+        <v>3433.3</v>
       </c>
       <c r="AH11">
-        <v>0.5290922415899065</v>
+        <v>0.6935545011306746</v>
       </c>
       <c r="AI11">
-        <v>0.5818977779182604</v>
+        <v>0.6334495355889305</v>
       </c>
       <c r="AJ11">
-        <v>0.3714636438613653</v>
+        <v>0.594232999290375</v>
       </c>
       <c r="AK11">
-        <v>0.4226572388808869</v>
+        <v>0.5279076203948582</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1814,7 +1811,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Burgan Bank K.P.S.C. (KWSE:BURG)</t>
+          <t>Kuwait Projects Company Holding K.S.C.P. (KWSE:KPROJ)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1823,13 +1820,7 @@
         </is>
       </c>
       <c r="D12">
-        <v>-0.0397</v>
-      </c>
-      <c r="E12">
-        <v>-0.08839999999999999</v>
-      </c>
-      <c r="F12">
-        <v>0.128</v>
+        <v>0.0124</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1838,34 +1829,34 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>0.003472263671469895</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>0.001736131835734948</v>
       </c>
       <c r="K12">
-        <v>137.1</v>
+        <v>-11.2</v>
       </c>
       <c r="L12">
-        <v>0.2840273461777502</v>
+        <v>-0.008119472234304769</v>
       </c>
       <c r="M12">
-        <v>72.3</v>
+        <v>40.7</v>
       </c>
       <c r="N12">
-        <v>0.02786878926878156</v>
+        <v>0.04557670772676372</v>
       </c>
       <c r="O12">
-        <v>0.5273522975929978</v>
+        <v>-3.633928571428572</v>
       </c>
       <c r="P12">
-        <v>72.3</v>
+        <v>40.7</v>
       </c>
       <c r="Q12">
-        <v>0.02786878926878156</v>
+        <v>0.04557670772676372</v>
       </c>
       <c r="R12">
-        <v>0.5273522975929978</v>
+        <v>-3.633928571428572</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1874,55 +1865,55 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>1988.8</v>
+        <v>3750.2</v>
       </c>
       <c r="V12">
-        <v>0.7666037081293604</v>
+        <v>4.199552071668533</v>
       </c>
       <c r="W12">
-        <v>0.04906065485775631</v>
+        <v>-0.009209768933475866</v>
       </c>
       <c r="X12">
-        <v>0.08183057938108843</v>
+        <v>0.3902490948155258</v>
       </c>
       <c r="Y12">
-        <v>-0.03276992452333212</v>
+        <v>-0.3994588637490016</v>
       </c>
       <c r="Z12">
-        <v>0.1119537990537156</v>
+        <v>0.1994447299827218</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>0.0003462623451925637</v>
       </c>
       <c r="AB12">
-        <v>0.04943160068644792</v>
+        <v>0.09754533917698112</v>
       </c>
       <c r="AC12">
-        <v>-0.04943160068644792</v>
+        <v>-0.09719907683178855</v>
       </c>
       <c r="AD12">
-        <v>4286.8</v>
+        <v>10620.2</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>9.001797457872131</v>
       </c>
       <c r="AF12">
-        <v>4286.8</v>
+        <v>10629.20179745787</v>
       </c>
       <c r="AG12">
-        <v>2298</v>
+        <v>6879.001797457872</v>
       </c>
       <c r="AH12">
-        <v>0.6229817907020679</v>
+        <v>0.9224974518154142</v>
       </c>
       <c r="AI12">
-        <v>0.5943487785264676</v>
+        <v>0.7616604751173572</v>
       </c>
       <c r="AJ12">
-        <v>0.4697177196819491</v>
+        <v>0.8851003868408664</v>
       </c>
       <c r="AK12">
-        <v>0.4399096443202267</v>
+        <v>0.6740747847484928</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1930,133 +1921,11 @@
       <c r="AM12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Kuwait</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Kuwait Projects Company Holding K.S.C.P. (KWSE:KPROJ)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D13">
-        <v>0.0331</v>
-      </c>
-      <c r="E13">
-        <v>-0.266</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0.003000176257192161</v>
-      </c>
-      <c r="J13">
-        <v>0.0022683215639256</v>
-      </c>
-      <c r="K13">
-        <v>38.4</v>
-      </c>
-      <c r="L13">
-        <v>0.02465331278890601</v>
-      </c>
-      <c r="M13">
-        <v>31.027</v>
-      </c>
-      <c r="N13">
-        <v>0.02548000328488133</v>
-      </c>
-      <c r="O13">
-        <v>0.8079947916666667</v>
-      </c>
-      <c r="P13">
-        <v>30.4</v>
-      </c>
-      <c r="Q13">
-        <v>0.02496509813582984</v>
-      </c>
-      <c r="R13">
-        <v>0.7916666666666666</v>
-      </c>
-      <c r="S13">
-        <v>0.6269999999999989</v>
-      </c>
-      <c r="T13">
-        <v>0.02020820575627676</v>
-      </c>
-      <c r="U13">
-        <v>3715.7</v>
-      </c>
-      <c r="V13">
-        <v>3.051408392871807</v>
-      </c>
-      <c r="W13">
-        <v>0.03307778447756051</v>
-      </c>
-      <c r="X13">
-        <v>0.2252858252194881</v>
-      </c>
-      <c r="Y13">
-        <v>-0.1922080407419276</v>
-      </c>
-      <c r="Z13">
-        <v>0.2665601235158625</v>
-      </c>
-      <c r="AA13">
-        <v>0.0006046440762537023</v>
-      </c>
-      <c r="AB13">
-        <v>0.06274167974461077</v>
-      </c>
-      <c r="AC13">
-        <v>-0.06213703566835707</v>
-      </c>
-      <c r="AD13">
-        <v>9406.799999999999</v>
-      </c>
-      <c r="AE13">
-        <v>10.63462730898745</v>
-      </c>
-      <c r="AF13">
-        <v>9417.434627308987</v>
-      </c>
-      <c r="AG13">
-        <v>5701.734627308987</v>
-      </c>
-      <c r="AH13">
-        <v>0.8855021546343964</v>
-      </c>
-      <c r="AI13">
-        <v>0.7588380901983004</v>
-      </c>
-      <c r="AJ13">
-        <v>0.8240174139092096</v>
-      </c>
-      <c r="AK13">
-        <v>0.6557762196700483</v>
-      </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
-        <v>0</v>
-      </c>
-      <c r="AN13">
-        <v>1383.35294117647</v>
-      </c>
-      <c r="AP13">
-        <v>838.4903863689686</v>
+      <c r="AN12">
+        <v>1611.562974203339</v>
+      </c>
+      <c r="AP12">
+        <v>1043.854597489814</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/kuwait/kuwait_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/kuwait/kuwait_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0439</v>
+        <v>0.0891</v>
       </c>
       <c r="E2">
-        <v>0.0745</v>
+        <v>0.06415</v>
       </c>
       <c r="F2">
-        <v>0.189</v>
+        <v>-0.002500000000000002</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,91 +603,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.0005016591089305767</v>
+        <v>7.972730912911413e-05</v>
       </c>
       <c r="J2">
-        <v>0.0004313894322071127</v>
+        <v>6.899023928973351e-05</v>
       </c>
       <c r="K2">
-        <v>3311.7</v>
+        <v>5060.1</v>
       </c>
       <c r="L2">
-        <v>0.3468620386275085</v>
+        <v>0.3731994955268573</v>
       </c>
       <c r="M2">
-        <v>2244.987</v>
+        <v>3450.8</v>
       </c>
       <c r="N2">
-        <v>0.02655648520221491</v>
+        <v>0.04455180302597993</v>
       </c>
       <c r="O2">
-        <v>0.677895642721261</v>
+        <v>0.6819628070591489</v>
       </c>
       <c r="P2">
-        <v>1843.5</v>
+        <v>2745.2</v>
       </c>
       <c r="Q2">
-        <v>0.02180719998391224</v>
+        <v>0.03544210318387624</v>
       </c>
       <c r="R2">
-        <v>0.5566627411903252</v>
+        <v>0.5425189225509377</v>
       </c>
       <c r="S2">
-        <v>401.487</v>
+        <v>705.5999999999999</v>
       </c>
       <c r="T2">
-        <v>0.1788371157605812</v>
+        <v>0.2044743247942506</v>
       </c>
       <c r="U2">
-        <v>32876.2</v>
+        <v>34549.3</v>
       </c>
       <c r="V2">
-        <v>0.3889003895368025</v>
+        <v>0.4460512368973828</v>
       </c>
       <c r="W2">
-        <v>0.06098694676515504</v>
+        <v>0.06446974620707251</v>
       </c>
       <c r="X2">
-        <v>0.0944958016652722</v>
+        <v>0.07847307527764726</v>
       </c>
       <c r="Y2">
-        <v>-0.03350885490011717</v>
+        <v>-0.01400332907057475</v>
       </c>
       <c r="Z2">
-        <v>0.1649889957237101</v>
+        <v>0.2324487575519857</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07332101501507307</v>
+        <v>0.06302716756083876</v>
       </c>
       <c r="AC2">
-        <v>-0.07332101501507307</v>
+        <v>-0.06302716756083876</v>
       </c>
       <c r="AD2">
-        <v>56132.4</v>
+        <v>72780.8</v>
       </c>
       <c r="AE2">
-        <v>9.001797457872131</v>
+        <v>6.245006668555402</v>
       </c>
       <c r="AF2">
-        <v>56141.40179745787</v>
+        <v>72787.04500666856</v>
       </c>
       <c r="AG2">
-        <v>23265.20179745788</v>
+        <v>38237.74500666856</v>
       </c>
       <c r="AH2">
-        <v>0.3990781842476217</v>
+        <v>0.484462315374861</v>
       </c>
       <c r="AI2">
-        <v>0.581163693318447</v>
+        <v>0.5677455192703961</v>
       </c>
       <c r="AJ2">
-        <v>0.2158151918993628</v>
+        <v>0.330508603168865</v>
       </c>
       <c r="AK2">
-        <v>0.3650846386647985</v>
+        <v>0.4082858622730839</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>8517.814871016692</v>
+        <v>31236.39484978541</v>
       </c>
       <c r="AP2">
-        <v>3530.379635426082</v>
+        <v>16411.04935908522</v>
       </c>
     </row>
     <row r="3">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.00993</v>
+        <v>-0.0264</v>
       </c>
       <c r="E3">
-        <v>-0.035</v>
+        <v>-0.0361</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -737,85 +737,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>111.3</v>
+        <v>127.7</v>
       </c>
       <c r="L3">
-        <v>0.4666666666666667</v>
+        <v>0.5017681728880157</v>
       </c>
       <c r="M3">
-        <v>218</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="N3">
-        <v>0.1045112421496716</v>
+        <v>0.04237596959758447</v>
       </c>
       <c r="O3">
-        <v>1.958670260557053</v>
+        <v>0.6374314800313234</v>
       </c>
       <c r="P3">
-        <v>61.7</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="Q3">
-        <v>0.02957955798456302</v>
+        <v>0.04237596959758447</v>
       </c>
       <c r="R3">
-        <v>0.5543575920934412</v>
+        <v>0.6374314800313234</v>
       </c>
       <c r="S3">
-        <v>156.3</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.7169724770642202</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>591.2</v>
+        <v>1253.6</v>
       </c>
       <c r="V3">
-        <v>0.2834268181600268</v>
+        <v>0.6526107553750845</v>
       </c>
       <c r="W3">
-        <v>0.04818181818181818</v>
+        <v>0.05971196109604415</v>
       </c>
       <c r="X3">
-        <v>0.07041257893186294</v>
+        <v>0.06233847710802748</v>
       </c>
       <c r="Y3">
-        <v>-0.02223076075004476</v>
+        <v>-0.002626516011983333</v>
       </c>
       <c r="Z3">
-        <v>0.1344419391206313</v>
+        <v>0.1644694325966137</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07041257893186294</v>
+        <v>0.0611497904970032</v>
       </c>
       <c r="AC3">
-        <v>-0.07041257893186294</v>
+        <v>-0.0611497904970032</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>139.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>139.8</v>
       </c>
       <c r="AG3">
-        <v>-591.2</v>
+        <v>-1113.8</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.06784102489445334</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.05983308367215922</v>
       </c>
       <c r="AJ3">
-        <v>-0.3955308757610223</v>
+        <v>-1.380002478007682</v>
       </c>
       <c r="AK3">
-        <v>-0.3820602300633321</v>
+        <v>-1.028534490719365</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -841,10 +841,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.09669999999999999</v>
+        <v>0.188</v>
       </c>
       <c r="E4">
-        <v>0.09329999999999999</v>
+        <v>0.233</v>
+      </c>
+      <c r="F4">
+        <v>0.29</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,85 +862,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>905.7</v>
+        <v>1984.6</v>
       </c>
       <c r="L4">
-        <v>0.3332842686292549</v>
+        <v>0.4156404456731171</v>
       </c>
       <c r="M4">
-        <v>360.987</v>
+        <v>1359.3</v>
       </c>
       <c r="N4">
-        <v>0.01009203371587526</v>
+        <v>0.03949627933600457</v>
       </c>
       <c r="O4">
-        <v>0.3985723749585955</v>
+        <v>0.6849239141388693</v>
       </c>
       <c r="P4">
-        <v>360.7</v>
+        <v>1183</v>
       </c>
       <c r="Q4">
-        <v>0.01008401012035393</v>
+        <v>0.03437364706429295</v>
       </c>
       <c r="R4">
-        <v>0.3982554929888484</v>
+        <v>0.5960898921697068</v>
       </c>
       <c r="S4">
-        <v>0.2869999999999777</v>
+        <v>176.3</v>
       </c>
       <c r="T4">
-        <v>0.0007950424807540929</v>
+        <v>0.1296991098359449</v>
       </c>
       <c r="U4">
-        <v>7257.5</v>
+        <v>9640</v>
       </c>
       <c r="V4">
-        <v>0.2028963222857463</v>
+        <v>0.2801030918848555</v>
       </c>
       <c r="W4">
-        <v>0.1267422334172964</v>
+        <v>0.2759263121306917</v>
       </c>
       <c r="X4">
-        <v>0.07873194262366122</v>
+        <v>0.07589127809530477</v>
       </c>
       <c r="Y4">
-        <v>0.04801029079363518</v>
+        <v>0.2000350340353869</v>
       </c>
       <c r="Z4">
-        <v>0.4155643570412735</v>
+        <v>0.4336981697624779</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.07135758704624885</v>
+        <v>0.06215688864002151</v>
       </c>
       <c r="AC4">
-        <v>-0.07135758704624885</v>
+        <v>-0.06215688864002151</v>
       </c>
       <c r="AD4">
-        <v>11074.5</v>
+        <v>27259.5</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>11074.5</v>
+        <v>27259.5</v>
       </c>
       <c r="AG4">
-        <v>3817</v>
+        <v>17619.5</v>
       </c>
       <c r="AH4">
-        <v>0.2364123473657245</v>
+        <v>0.4419833515469701</v>
       </c>
       <c r="AI4">
-        <v>0.5826139107652973</v>
+        <v>0.5826559424087686</v>
       </c>
       <c r="AJ4">
-        <v>0.09642175994341505</v>
+        <v>0.3386060258977542</v>
       </c>
       <c r="AK4">
-        <v>0.3248289478163189</v>
+        <v>0.4743450648675861</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -963,10 +966,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.197</v>
+        <v>0.14</v>
       </c>
       <c r="E5">
-        <v>0.276</v>
+        <v>0.11</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -981,85 +984,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>72.2</v>
+        <v>58.1</v>
       </c>
       <c r="L5">
-        <v>0.386509635974304</v>
+        <v>0.3128702207862143</v>
       </c>
       <c r="M5">
-        <v>257.3</v>
+        <v>26.6</v>
       </c>
       <c r="N5">
-        <v>0.1678736869576564</v>
+        <v>0.0213260642988856</v>
       </c>
       <c r="O5">
-        <v>3.563711911357341</v>
+        <v>0.4578313253012049</v>
       </c>
       <c r="P5">
-        <v>12.4</v>
+        <v>26.6</v>
       </c>
       <c r="Q5">
-        <v>0.008090298166634044</v>
+        <v>0.0213260642988856</v>
       </c>
       <c r="R5">
-        <v>0.1717451523545706</v>
+        <v>0.4578313253012049</v>
       </c>
       <c r="S5">
-        <v>244.9</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>0.9518072289156626</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>1351.8</v>
+        <v>803.9</v>
       </c>
       <c r="V5">
-        <v>0.8819729888432178</v>
+        <v>0.6445121462358695</v>
       </c>
       <c r="W5">
-        <v>0.07925356750823272</v>
+        <v>0.049434187016081</v>
       </c>
       <c r="X5">
-        <v>0.08770926113845887</v>
+        <v>0.07592998093266437</v>
       </c>
       <c r="Y5">
-        <v>-0.008455693630226149</v>
+        <v>-0.02649579391658337</v>
       </c>
       <c r="Z5">
-        <v>0.2799760191846523</v>
+        <v>0.2292309591408468</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.07197798353632466</v>
+        <v>0.06215860831038355</v>
       </c>
       <c r="AC5">
-        <v>-0.07197798353632466</v>
+        <v>-0.06215860831038355</v>
       </c>
       <c r="AD5">
-        <v>986.6</v>
+        <v>990.5</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>986.6</v>
+        <v>990.5</v>
       </c>
       <c r="AG5">
-        <v>-365.1999999999999</v>
+        <v>186.6</v>
       </c>
       <c r="AH5">
-        <v>0.3916167189298614</v>
+        <v>0.442622218250067</v>
       </c>
       <c r="AI5">
-        <v>0.4563578333872982</v>
+        <v>0.4453086364249426</v>
       </c>
       <c r="AJ5">
-        <v>-0.3128051391862954</v>
+        <v>0.1301345979496478</v>
       </c>
       <c r="AK5">
-        <v>-0.4508085421552894</v>
+        <v>0.1313714446634751</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1085,10 +1088,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.105</v>
+        <v>0.08439999999999999</v>
       </c>
       <c r="E6">
-        <v>0.0745</v>
+        <v>0.0548</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1103,28 +1106,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>210.1</v>
+        <v>227.4</v>
       </c>
       <c r="L6">
-        <v>0.4034178187403994</v>
+        <v>0.4101731601731602</v>
       </c>
       <c r="M6">
-        <v>80.40000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="N6">
-        <v>0.008264802631578949</v>
+        <v>0.01191337605954104</v>
       </c>
       <c r="O6">
-        <v>0.3826749167063304</v>
+        <v>0.405452946350044</v>
       </c>
       <c r="P6">
-        <v>80.40000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="Q6">
-        <v>0.008264802631578949</v>
+        <v>0.01191337605954104</v>
       </c>
       <c r="R6">
-        <v>0.3826749167063304</v>
+        <v>0.405452946350044</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1133,55 +1136,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>2202.3</v>
+        <v>2211.3</v>
       </c>
       <c r="V6">
-        <v>0.2263877467105263</v>
+        <v>0.2857272069464544</v>
       </c>
       <c r="W6">
-        <v>0.09031509263637535</v>
+        <v>0.07483955899292415</v>
       </c>
       <c r="X6">
-        <v>0.07815530477513177</v>
+        <v>0.06710585994055335</v>
       </c>
       <c r="Y6">
-        <v>0.01215978786124358</v>
+        <v>0.007733699052370799</v>
       </c>
       <c r="Z6">
-        <v>0.2096196417790299</v>
+        <v>0.152336987882285</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.07239052308785689</v>
+        <v>0.06256377637079072</v>
       </c>
       <c r="AC6">
-        <v>-0.07239052308785689</v>
+        <v>-0.06256377637079072</v>
       </c>
       <c r="AD6">
-        <v>2803.1</v>
+        <v>2521.4</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>2803.1</v>
+        <v>2521.4</v>
       </c>
       <c r="AG6">
-        <v>600.7999999999997</v>
+        <v>310.0999999999999</v>
       </c>
       <c r="AH6">
-        <v>0.2236914556583221</v>
+        <v>0.2457361167962887</v>
       </c>
       <c r="AI6">
-        <v>0.4722362613295596</v>
+        <v>0.4356103797380878</v>
       </c>
       <c r="AJ6">
-        <v>0.05816745410889937</v>
+        <v>0.03852508913818592</v>
       </c>
       <c r="AK6">
-        <v>0.1609213874380608</v>
+        <v>0.08669518297967511</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1207,10 +1210,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0545</v>
+        <v>0.0398</v>
       </c>
       <c r="E7">
-        <v>-0.00646</v>
+        <v>-0.0162</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1225,85 +1228,85 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>108.4</v>
+        <v>121.1</v>
       </c>
       <c r="L7">
-        <v>0.2695846804277543</v>
+        <v>0.2824160447761194</v>
       </c>
       <c r="M7">
-        <v>48.8</v>
+        <v>367.4</v>
       </c>
       <c r="N7">
-        <v>0.02608649168760357</v>
+        <v>0.2053431701319025</v>
       </c>
       <c r="O7">
-        <v>0.4501845018450184</v>
+        <v>3.033856317093311</v>
       </c>
       <c r="P7">
-        <v>48.8</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="Q7">
-        <v>0.02608649168760357</v>
+        <v>0.03778224904985468</v>
       </c>
       <c r="R7">
-        <v>0.4501845018450184</v>
+        <v>0.5582163501238645</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>299.8</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>0.8160043549265106</v>
       </c>
       <c r="U7">
-        <v>1473.1</v>
+        <v>341.4</v>
       </c>
       <c r="V7">
-        <v>0.787459239856738</v>
+        <v>0.1908115358819584</v>
       </c>
       <c r="W7">
-        <v>0.05453264915987524</v>
+        <v>0.06275912106135986</v>
       </c>
       <c r="X7">
-        <v>0.1202742528823892</v>
+        <v>0.1136496639966621</v>
       </c>
       <c r="Y7">
-        <v>-0.06574160372251393</v>
+        <v>-0.05089054293530224</v>
       </c>
       <c r="Z7">
-        <v>0.1252179870453413</v>
+        <v>0.1091705280309588</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.07301006751330517</v>
+        <v>0.06294982835484263</v>
       </c>
       <c r="AC7">
-        <v>-0.07301006751330517</v>
+        <v>-0.06294982835484263</v>
       </c>
       <c r="AD7">
-        <v>3471.3</v>
+        <v>5002.6</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>3471.3</v>
+        <v>5002.6</v>
       </c>
       <c r="AG7">
-        <v>1998.2</v>
+        <v>4661.200000000001</v>
       </c>
       <c r="AH7">
-        <v>0.6498128041931861</v>
+        <v>0.7365646809387791</v>
       </c>
       <c r="AI7">
-        <v>0.6422030229589477</v>
+        <v>0.719094986200552</v>
       </c>
       <c r="AJ7">
-        <v>0.5164775517588979</v>
+        <v>0.7226218529083468</v>
       </c>
       <c r="AK7">
-        <v>0.5081633691063527</v>
+        <v>0.7045983613991595</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1329,10 +1332,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0108</v>
+        <v>0.0268</v>
       </c>
       <c r="E8">
-        <v>-0.0949</v>
+        <v>-0.0355</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1347,28 +1350,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>35.6</v>
+        <v>53.2</v>
       </c>
       <c r="L8">
-        <v>0.1993281075027996</v>
+        <v>0.255278310940499</v>
       </c>
       <c r="M8">
-        <v>29.8</v>
+        <v>30.5</v>
       </c>
       <c r="N8">
-        <v>0.04396577161404545</v>
+        <v>0.04078630649906392</v>
       </c>
       <c r="O8">
-        <v>0.8370786516853932</v>
+        <v>0.5733082706766917</v>
       </c>
       <c r="P8">
-        <v>29.8</v>
+        <v>30.5</v>
       </c>
       <c r="Q8">
-        <v>0.04396577161404545</v>
+        <v>0.04078630649906392</v>
       </c>
       <c r="R8">
-        <v>0.8370786516853932</v>
+        <v>0.5733082706766917</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1377,55 +1380,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>443.1</v>
+        <v>604.6</v>
       </c>
       <c r="V8">
-        <v>0.6537326645028033</v>
+        <v>0.808504947847018</v>
       </c>
       <c r="W8">
-        <v>0.03058944835882454</v>
+        <v>0.04941023497724529</v>
       </c>
       <c r="X8">
-        <v>0.1816179173613457</v>
+        <v>0.1336042652600188</v>
       </c>
       <c r="Y8">
-        <v>-0.1510284690025211</v>
+        <v>-0.0841940302827735</v>
       </c>
       <c r="Z8">
-        <v>0.08220565221393722</v>
+        <v>0.06060429813592345</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.07363196251684097</v>
+        <v>0.06310450676683488</v>
       </c>
       <c r="AC8">
-        <v>-0.07363196251684097</v>
+        <v>-0.06310450676683488</v>
       </c>
       <c r="AD8">
-        <v>2805.1</v>
+        <v>2882.8</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>2805.1</v>
+        <v>2882.8</v>
       </c>
       <c r="AG8">
-        <v>2362</v>
+        <v>2278.2</v>
       </c>
       <c r="AH8">
-        <v>0.8053920583421862</v>
+        <v>0.7940285352283368</v>
       </c>
       <c r="AI8">
-        <v>0.7204386685843436</v>
+        <v>0.6855485006301871</v>
       </c>
       <c r="AJ8">
-        <v>0.7770248042634383</v>
+        <v>0.7528750826173167</v>
       </c>
       <c r="AK8">
-        <v>0.6845384726851181</v>
+        <v>0.6327454520205528</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1451,13 +1454,13 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0824</v>
+        <v>0.09380000000000001</v>
       </c>
       <c r="E9">
-        <v>0.0892</v>
+        <v>0.0969</v>
       </c>
       <c r="F9">
-        <v>0.189</v>
+        <v>-0.295</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1472,28 +1475,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>1552</v>
+        <v>1830.9</v>
       </c>
       <c r="L9">
-        <v>0.518976759739174</v>
+        <v>0.5259695489801781</v>
       </c>
       <c r="M9">
-        <v>1002.7</v>
+        <v>926</v>
       </c>
       <c r="N9">
-        <v>0.0377671895892578</v>
+        <v>0.04012583739936041</v>
       </c>
       <c r="O9">
-        <v>0.646069587628866</v>
+        <v>0.5057621934567699</v>
       </c>
       <c r="P9">
-        <v>1002.7</v>
+        <v>926</v>
       </c>
       <c r="Q9">
-        <v>0.0377671895892578</v>
+        <v>0.04012583739936041</v>
       </c>
       <c r="R9">
-        <v>0.646069587628866</v>
+        <v>0.5057621934567699</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1502,55 +1505,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>12328.9</v>
+        <v>11773.8</v>
       </c>
       <c r="V9">
-        <v>0.4643740936740805</v>
+        <v>0.5101874561259067</v>
       </c>
       <c r="W9">
-        <v>0.1206739703446828</v>
+        <v>0.1445523448602558</v>
       </c>
       <c r="X9">
-        <v>0.08612215947066411</v>
+        <v>0.07392731973523892</v>
       </c>
       <c r="Y9">
-        <v>0.03455181087401869</v>
+        <v>0.07062502512501689</v>
       </c>
       <c r="Z9">
-        <v>0.1223518726116734</v>
+        <v>0.2194981997490368</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.07367485553575144</v>
+        <v>0.0636149373195949</v>
       </c>
       <c r="AC9">
-        <v>-0.07367485553575144</v>
+        <v>-0.0636149373195949</v>
       </c>
       <c r="AD9">
-        <v>15521.8</v>
+        <v>15873.3</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>15521.8</v>
+        <v>15873.3</v>
       </c>
       <c r="AG9">
-        <v>3192.9</v>
+        <v>4099.5</v>
       </c>
       <c r="AH9">
-        <v>0.3689403465070012</v>
+        <v>0.4075228429784317</v>
       </c>
       <c r="AI9">
-        <v>0.5170796383527327</v>
+        <v>0.5073027459603191</v>
       </c>
       <c r="AJ9">
-        <v>0.1073517940717629</v>
+        <v>0.1508450191154988</v>
       </c>
       <c r="AK9">
-        <v>0.1804989456903326</v>
+        <v>0.2100605663103742</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1576,10 +1579,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.0333</v>
+        <v>0.12</v>
       </c>
       <c r="E10">
-        <v>0.08169999999999999</v>
+        <v>0.185</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1594,85 +1597,85 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>178.2</v>
+        <v>424.6</v>
       </c>
       <c r="L10">
-        <v>0.5198366394399067</v>
+        <v>0.7278025368529312</v>
       </c>
       <c r="M10">
-        <v>127.7</v>
+        <v>453.9</v>
       </c>
       <c r="N10">
-        <v>0.04139652489626556</v>
+        <v>0.1495551894563427</v>
       </c>
       <c r="O10">
-        <v>0.7166105499438833</v>
+        <v>1.069006123410268</v>
       </c>
       <c r="P10">
-        <v>127.7</v>
+        <v>224.4</v>
       </c>
       <c r="Q10">
-        <v>0.04139652489626556</v>
+        <v>0.07393739703459638</v>
       </c>
       <c r="R10">
-        <v>0.7166105499438833</v>
+        <v>0.5284974093264249</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>229.5</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>0.5056179775280899</v>
       </c>
       <c r="U10">
-        <v>1605.5</v>
+        <v>1549.4</v>
       </c>
       <c r="V10">
-        <v>0.5204551348547718</v>
+        <v>0.510510708401977</v>
       </c>
       <c r="W10">
-        <v>0.06744124437043483</v>
+        <v>0.1962469957478277</v>
       </c>
       <c r="X10">
-        <v>0.1012823421920855</v>
+        <v>0.08101616962263014</v>
       </c>
       <c r="Y10">
-        <v>-0.03384109782165071</v>
+        <v>0.1152308261251976</v>
       </c>
       <c r="Z10">
-        <v>0.07486350731600785</v>
+        <v>0.1422233057045344</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.0777756530749894</v>
+        <v>0.06607110024897338</v>
       </c>
       <c r="AC10">
-        <v>-0.0777756530749894</v>
+        <v>-0.06607110024897338</v>
       </c>
       <c r="AD10">
-        <v>3543.9</v>
+        <v>3229.4</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>3543.9</v>
+        <v>3229.4</v>
       </c>
       <c r="AG10">
-        <v>1938.4</v>
+        <v>1680</v>
       </c>
       <c r="AH10">
-        <v>0.5346297162339523</v>
+        <v>0.5155162505587128</v>
       </c>
       <c r="AI10">
-        <v>0.6208110712095998</v>
+        <v>0.5995358767288592</v>
       </c>
       <c r="AJ10">
-        <v>0.3858894728459946</v>
+        <v>0.3563096500530223</v>
       </c>
       <c r="AK10">
-        <v>0.4724348038020961</v>
+        <v>0.4378306533580048</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1698,10 +1701,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>-0.0154</v>
+        <v>0.00428</v>
       </c>
       <c r="E11">
-        <v>-0.08800000000000001</v>
+        <v>-0.13</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1716,28 +1719,28 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>149.4</v>
+        <v>132.7</v>
       </c>
       <c r="L11">
-        <v>0.2529630883846936</v>
+        <v>0.1929620474043914</v>
       </c>
       <c r="M11">
-        <v>78.59999999999999</v>
+        <v>113.5</v>
       </c>
       <c r="N11">
-        <v>0.03352670192799863</v>
+        <v>0.05881133737499352</v>
       </c>
       <c r="O11">
-        <v>0.5261044176706827</v>
+        <v>0.8553127354935947</v>
       </c>
       <c r="P11">
-        <v>78.59999999999999</v>
+        <v>113.5</v>
       </c>
       <c r="Q11">
-        <v>0.03352670192799863</v>
+        <v>0.05881133737499352</v>
       </c>
       <c r="R11">
-        <v>0.5261044176706827</v>
+        <v>0.8553127354935947</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1746,55 +1749,55 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>1872.6</v>
+        <v>1569.4</v>
       </c>
       <c r="V11">
-        <v>0.7987544787578911</v>
+        <v>0.813202756619514</v>
       </c>
       <c r="W11">
-        <v>0.05365801099019502</v>
+        <v>0.0455137878995747</v>
       </c>
       <c r="X11">
-        <v>0.1312269472868304</v>
+        <v>0.1040094575439404</v>
       </c>
       <c r="Y11">
-        <v>-0.07756893629663542</v>
+        <v>-0.05849566964436569</v>
       </c>
       <c r="Z11">
-        <v>0.1162072290104874</v>
+        <v>0.1083179763423585</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.07884432037971015</v>
+        <v>0.06706406858789038</v>
       </c>
       <c r="AC11">
-        <v>-0.07884432037971015</v>
+        <v>-0.06706406858789038</v>
       </c>
       <c r="AD11">
-        <v>5305.9</v>
+        <v>4408.6</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>5305.9</v>
+        <v>4408.6</v>
       </c>
       <c r="AG11">
-        <v>3433.3</v>
+        <v>2839.2</v>
       </c>
       <c r="AH11">
-        <v>0.6935545011306746</v>
+        <v>0.6955273329652126</v>
       </c>
       <c r="AI11">
-        <v>0.6334495355889305</v>
+        <v>0.593119778283039</v>
       </c>
       <c r="AJ11">
-        <v>0.594232999290375</v>
+        <v>0.5953324526640247</v>
       </c>
       <c r="AK11">
-        <v>0.5279076203948582</v>
+        <v>0.4842159119979535</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1820,7 +1823,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.0124</v>
+        <v>0.111</v>
+      </c>
+      <c r="E12">
+        <v>0.0735</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1829,91 +1835,88 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0.003472263671469895</v>
+        <v>0.0004504161109537166</v>
       </c>
       <c r="J12">
-        <v>0.001736131835734948</v>
+        <v>0.0002257869964935083</v>
       </c>
       <c r="K12">
-        <v>-11.2</v>
+        <v>99.8</v>
       </c>
       <c r="L12">
-        <v>-0.008119472234304769</v>
+        <v>0.04158333333333333</v>
       </c>
       <c r="M12">
-        <v>40.7</v>
+        <v>-0</v>
       </c>
       <c r="N12">
-        <v>0.04557670772676372</v>
+        <v>-0</v>
       </c>
       <c r="O12">
-        <v>-3.633928571428572</v>
+        <v>-0</v>
       </c>
       <c r="P12">
-        <v>40.7</v>
+        <v>-0</v>
       </c>
       <c r="Q12">
-        <v>0.04557670772676372</v>
+        <v>-0</v>
       </c>
       <c r="R12">
-        <v>-3.633928571428572</v>
+        <v>-0</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
       <c r="U12">
-        <v>3750.2</v>
+        <v>4801.9</v>
       </c>
       <c r="V12">
-        <v>4.199552071668533</v>
+        <v>3.091418270778343</v>
       </c>
       <c r="W12">
-        <v>-0.009209768933475866</v>
+        <v>0.06618037135278515</v>
       </c>
       <c r="X12">
-        <v>0.3902490948155258</v>
+        <v>0.1880830767790113</v>
       </c>
       <c r="Y12">
-        <v>-0.3994588637490016</v>
+        <v>-0.1219027054262262</v>
       </c>
       <c r="Z12">
-        <v>0.1994447299827218</v>
+        <v>0.3138385128117578</v>
       </c>
       <c r="AA12">
-        <v>0.0003462623451925637</v>
+        <v>7.086065519175621e-05</v>
       </c>
       <c r="AB12">
-        <v>0.09754533917698112</v>
+        <v>0.06761390205134787</v>
       </c>
       <c r="AC12">
-        <v>-0.09719907683178855</v>
+        <v>-0.06754304139615612</v>
       </c>
       <c r="AD12">
-        <v>10620.2</v>
+        <v>10472.9</v>
       </c>
       <c r="AE12">
-        <v>9.001797457872131</v>
+        <v>6.245006668555402</v>
       </c>
       <c r="AF12">
-        <v>10629.20179745787</v>
+        <v>10479.14500666856</v>
       </c>
       <c r="AG12">
-        <v>6879.001797457872</v>
+        <v>5677.245006668556</v>
       </c>
       <c r="AH12">
-        <v>0.9224974518154142</v>
+        <v>0.8709073676098966</v>
       </c>
       <c r="AI12">
-        <v>0.7616604751173572</v>
+        <v>0.663285512469133</v>
       </c>
       <c r="AJ12">
-        <v>0.8851003868408664</v>
+        <v>0.7851752532392192</v>
       </c>
       <c r="AK12">
-        <v>0.6740747847484928</v>
+        <v>0.5162565606380562</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1922,10 +1925,10 @@
         <v>0</v>
       </c>
       <c r="AN12">
-        <v>1611.562974203339</v>
+        <v>4494.806866952789</v>
       </c>
       <c r="AP12">
-        <v>1043.854597489814</v>
+        <v>2436.585839771913</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/kuwait/kuwait_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/kuwait/kuwait_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0897</v>
+        <v>0.08990000000000001</v>
       </c>
       <c r="E2">
-        <v>0.0793</v>
+        <v>0.0876</v>
       </c>
       <c r="F2">
-        <v>0.09670000000000001</v>
+        <v>0.0709</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>2371.4</v>
+        <v>5294.3</v>
       </c>
       <c r="L2">
-        <v>0.4618380820690596</v>
+        <v>0.3562977818455906</v>
       </c>
       <c r="M2">
-        <v>1207.4</v>
+        <v>3235.335</v>
       </c>
       <c r="N2">
-        <v>0.03560024177735844</v>
+        <v>0.03689846616356132</v>
       </c>
       <c r="O2">
-        <v>0.5091507126591887</v>
+        <v>0.6110977844096481</v>
       </c>
       <c r="P2">
-        <v>1207.4</v>
+        <v>2746.995</v>
       </c>
       <c r="Q2">
-        <v>0.03560024177735844</v>
+        <v>0.03132902838777812</v>
       </c>
       <c r="R2">
-        <v>0.5091507126591887</v>
+        <v>0.5188589615246586</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>488.34</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.1509395472184488</v>
       </c>
       <c r="U2">
-        <v>18043</v>
+        <v>42712.1</v>
       </c>
       <c r="V2">
-        <v>0.5319986436879892</v>
+        <v>0.4871245100197189</v>
       </c>
       <c r="W2">
-        <v>0.09500986749365661</v>
+        <v>0.08230309606143218</v>
       </c>
       <c r="X2">
-        <v>0.08110563726674122</v>
+        <v>0.08307957796610638</v>
       </c>
       <c r="Y2">
-        <v>0.01390423022691539</v>
+        <v>-0.0007764819046741922</v>
       </c>
       <c r="Z2">
-        <v>0.1904746006662363</v>
+        <v>0.1702769383795776</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06799592005577097</v>
+        <v>0.06740705914096329</v>
       </c>
       <c r="AC2">
-        <v>-0.06799592005577097</v>
+        <v>-0.06740705914096329</v>
       </c>
       <c r="AD2">
-        <v>26798.5</v>
+        <v>80828.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>26798.5</v>
+        <v>80828.7</v>
       </c>
       <c r="AG2">
-        <v>8755.5</v>
+        <v>38116.6</v>
       </c>
       <c r="AH2">
-        <v>0.4413891359488751</v>
+        <v>0.4796648048671064</v>
       </c>
       <c r="AI2">
-        <v>0.5363046541041609</v>
+        <v>0.5776465829471812</v>
       </c>
       <c r="AJ2">
-        <v>0.2051861920273722</v>
+        <v>0.3029967718267358</v>
       </c>
       <c r="AK2">
-        <v>0.2742452812458889</v>
+        <v>0.3920835669209128</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Boubyan Bank K.S.C.P. (KWSE:BOUBYAN)</t>
+          <t>Gulf Bank K.S.C.P. (KWSE:GBK)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,13 +713,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.114</v>
+        <v>0.0136</v>
       </c>
       <c r="E3">
-        <v>0.0876</v>
-      </c>
-      <c r="F3">
-        <v>0.16</v>
+        <v>0.0239</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,85 +731,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>303.3</v>
+        <v>188.1</v>
       </c>
       <c r="L3">
-        <v>0.4353380221042055</v>
+        <v>0.3838775510204082</v>
       </c>
       <c r="M3">
-        <v>123.3</v>
+        <v>149.66</v>
       </c>
       <c r="N3">
-        <v>0.01612903225806452</v>
+        <v>0.03730309072781655</v>
       </c>
       <c r="O3">
-        <v>0.4065281899109792</v>
+        <v>0.7956406166932483</v>
       </c>
       <c r="P3">
-        <v>123.3</v>
+        <v>141.9</v>
       </c>
       <c r="Q3">
-        <v>0.01612903225806452</v>
+        <v>0.03536889332003988</v>
       </c>
       <c r="R3">
-        <v>0.4065281899109792</v>
+        <v>0.7543859649122807</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>7.759999999999991</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.0518508619537618</v>
       </c>
       <c r="U3">
-        <v>1849.1</v>
+        <v>3867.4</v>
       </c>
       <c r="V3">
-        <v>0.2418831593543155</v>
+        <v>0.9639581256231307</v>
       </c>
       <c r="W3">
-        <v>0.09500986749365661</v>
+        <v>0.07856814669395598</v>
       </c>
       <c r="X3">
-        <v>0.07167652982629037</v>
+        <v>0.07371183737569487</v>
       </c>
       <c r="Y3">
-        <v>0.02333333766736624</v>
+        <v>0.004856309318261115</v>
       </c>
       <c r="Z3">
-        <v>0.1989207400639561</v>
+        <v>1.009476720230738</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.067274388074613</v>
+        <v>0.06685532491334976</v>
       </c>
       <c r="AC3">
-        <v>-0.067274388074613</v>
+        <v>-0.06685532491334976</v>
       </c>
       <c r="AD3">
-        <v>2216.5</v>
+        <v>1628.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2216.5</v>
+        <v>1628.8</v>
       </c>
       <c r="AG3">
-        <v>367.4000000000001</v>
+        <v>-2238.6</v>
       </c>
       <c r="AH3">
-        <v>0.2247720842502358</v>
+        <v>0.2887533683165509</v>
       </c>
       <c r="AI3">
-        <v>0.3898650906724359</v>
+        <v>0.3799925345278089</v>
       </c>
       <c r="AJ3">
-        <v>0.04585621567648528</v>
+        <v>-1.262320965377242</v>
       </c>
       <c r="AK3">
-        <v>0.09577185756738441</v>
+        <v>-5.342720763723157</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -829,7 +826,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>National Bank of Kuwait S.A.K.P. (KWSE:NBK)</t>
+          <t>Kuwait Finance House K.S.C.P. (KWSE:KFH)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -838,13 +835,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0897</v>
+        <v>0.178</v>
       </c>
       <c r="E4">
-        <v>0.0793</v>
+        <v>0.195</v>
       </c>
       <c r="F4">
-        <v>0.0334</v>
+        <v>0.0709</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,85 +856,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>1915.6</v>
+        <v>1978.8</v>
       </c>
       <c r="L4">
-        <v>0.5053686848700699</v>
+        <v>0.4003236900667611</v>
       </c>
       <c r="M4">
-        <v>978.7</v>
+        <v>1160.1</v>
       </c>
       <c r="N4">
-        <v>0.04043496403531604</v>
+        <v>0.02884959713518353</v>
       </c>
       <c r="O4">
-        <v>0.5109104197118397</v>
+        <v>0.5862644026682837</v>
       </c>
       <c r="P4">
-        <v>978.7</v>
+        <v>1059.6</v>
       </c>
       <c r="Q4">
-        <v>0.04043496403531604</v>
+        <v>0.02635034318113996</v>
       </c>
       <c r="R4">
-        <v>0.5109104197118397</v>
+        <v>0.5354760460885385</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>100.5</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.08663046289113008</v>
       </c>
       <c r="U4">
-        <v>14196.5</v>
+        <v>10500.2</v>
       </c>
       <c r="V4">
-        <v>0.5865280136174151</v>
+        <v>0.2611210583905302</v>
       </c>
       <c r="W4">
-        <v>0.1413351434305277</v>
+        <v>0.1068974458706081</v>
       </c>
       <c r="X4">
-        <v>0.08110563726674122</v>
+        <v>0.07897980645464314</v>
       </c>
       <c r="Y4">
-        <v>0.06022950616378644</v>
+        <v>0.02791763941596491</v>
       </c>
       <c r="Z4">
-        <v>0.2147214936753318</v>
+        <v>0.1368088633765745</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06799592005577097</v>
+        <v>0.06698666541602677</v>
       </c>
       <c r="AC4">
-        <v>-0.06799592005577097</v>
+        <v>-0.06698666541602677</v>
       </c>
       <c r="AD4">
-        <v>19951.3</v>
+        <v>28335.3</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>19951.3</v>
+        <v>28335.3</v>
       </c>
       <c r="AG4">
-        <v>5754.799999999999</v>
+        <v>17835.1</v>
       </c>
       <c r="AH4">
-        <v>0.4518407631195137</v>
+        <v>0.4133685790687598</v>
       </c>
       <c r="AI4">
-        <v>0.5489632287390352</v>
+        <v>0.5812118862572074</v>
       </c>
       <c r="AJ4">
-        <v>0.1920885473862699</v>
+        <v>0.3072522141502332</v>
       </c>
       <c r="AK4">
-        <v>0.2598444040077482</v>
+        <v>0.4662539638553902</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -954,117 +951,974 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Warba Bank K.S.C.P. (KWSE:WARBABANK)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.09449999999999999</v>
+      </c>
+      <c r="E5">
+        <v>0.0385</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="L5">
+        <v>0.3119395941481831</v>
+      </c>
+      <c r="M5">
+        <v>10.1</v>
+      </c>
+      <c r="N5">
+        <v>0.00742537862079106</v>
+      </c>
+      <c r="O5">
+        <v>0.1527987897125567</v>
+      </c>
+      <c r="P5">
+        <v>10.1</v>
+      </c>
+      <c r="Q5">
+        <v>0.00742537862079106</v>
+      </c>
+      <c r="R5">
+        <v>0.1527987897125567</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>584.8</v>
+      </c>
+      <c r="V5">
+        <v>0.4299367740038229</v>
+      </c>
+      <c r="W5">
+        <v>0.05357432322904847</v>
+      </c>
+      <c r="X5">
+        <v>0.07952882243743767</v>
+      </c>
+      <c r="Y5">
+        <v>-0.0259544992083892</v>
+      </c>
+      <c r="Z5">
+        <v>0.1491833286398198</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.06699775274683051</v>
+      </c>
+      <c r="AC5">
+        <v>-0.06699775274683051</v>
+      </c>
+      <c r="AD5">
+        <v>1000.8</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>1000.8</v>
+      </c>
+      <c r="AG5">
+        <v>416</v>
+      </c>
+      <c r="AH5">
+        <v>0.4238881829733164</v>
+      </c>
+      <c r="AI5">
+        <v>0.4270535523789204</v>
+      </c>
+      <c r="AJ5">
+        <v>0.2342078594752843</v>
+      </c>
+      <c r="AK5">
+        <v>0.23653835219196</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Boubyan Bank K.S.C.P. (KWSE:BOUBYAN)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.114</v>
+      </c>
+      <c r="E6">
+        <v>0.0876</v>
+      </c>
+      <c r="F6">
+        <v>0.16</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>303.3</v>
+      </c>
+      <c r="L6">
+        <v>0.4353380221042055</v>
+      </c>
+      <c r="M6">
+        <v>123.3</v>
+      </c>
+      <c r="N6">
+        <v>0.01612903225806452</v>
+      </c>
+      <c r="O6">
+        <v>0.4065281899109792</v>
+      </c>
+      <c r="P6">
+        <v>123.3</v>
+      </c>
+      <c r="Q6">
+        <v>0.01612903225806452</v>
+      </c>
+      <c r="R6">
+        <v>0.4065281899109792</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>1849.1</v>
+      </c>
+      <c r="V6">
+        <v>0.2418831593543155</v>
+      </c>
+      <c r="W6">
+        <v>0.09500986749365661</v>
+      </c>
+      <c r="X6">
+        <v>0.07166510513691335</v>
+      </c>
+      <c r="Y6">
+        <v>0.02334476235674326</v>
+      </c>
+      <c r="Z6">
+        <v>0.1989207400639561</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.06726553133647915</v>
+      </c>
+      <c r="AC6">
+        <v>-0.06726553133647915</v>
+      </c>
+      <c r="AD6">
+        <v>2216.5</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>2216.5</v>
+      </c>
+      <c r="AG6">
+        <v>367.4000000000001</v>
+      </c>
+      <c r="AH6">
+        <v>0.2247720842502358</v>
+      </c>
+      <c r="AI6">
+        <v>0.3898650906724359</v>
+      </c>
+      <c r="AJ6">
+        <v>0.04585621567648528</v>
+      </c>
+      <c r="AK6">
+        <v>0.09577185756738441</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kuwait International Bank K.S.C.P. (KWSE:KIB)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.06849999999999999</v>
+      </c>
+      <c r="E7">
+        <v>0.09359999999999999</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>93</v>
+      </c>
+      <c r="L7">
+        <v>0.3509433962264151</v>
+      </c>
+      <c r="M7">
+        <v>342.3</v>
+      </c>
+      <c r="N7">
+        <v>0.3654708520179372</v>
+      </c>
+      <c r="O7">
+        <v>3.680645161290323</v>
+      </c>
+      <c r="P7">
+        <v>42</v>
+      </c>
+      <c r="Q7">
+        <v>0.04484304932735426</v>
+      </c>
+      <c r="R7">
+        <v>0.4516129032258064</v>
+      </c>
+      <c r="S7">
+        <v>300.3</v>
+      </c>
+      <c r="T7">
+        <v>0.8773006134969326</v>
+      </c>
+      <c r="U7">
+        <v>180.5</v>
+      </c>
+      <c r="V7">
+        <v>0.1927183429425582</v>
+      </c>
+      <c r="W7">
+        <v>0.07093821510297482</v>
+      </c>
+      <c r="X7">
+        <v>0.1175130969368392</v>
+      </c>
+      <c r="Y7">
+        <v>-0.04657488183386441</v>
+      </c>
+      <c r="Z7">
+        <v>0.07383260893792488</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0.06733396325295168</v>
+      </c>
+      <c r="AC7">
+        <v>-0.06733396325295168</v>
+      </c>
+      <c r="AD7">
+        <v>2706.1</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>2706.1</v>
+      </c>
+      <c r="AG7">
+        <v>2525.6</v>
+      </c>
+      <c r="AH7">
+        <v>0.7428830263266258</v>
+      </c>
+      <c r="AI7">
+        <v>0.6493964627678721</v>
+      </c>
+      <c r="AJ7">
+        <v>0.7294783663566519</v>
+      </c>
+      <c r="AK7">
+        <v>0.6335222997040084</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kuwait Projects Company Holding K.S.C.P. (KWSE:KPROJ)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.168</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>100.8</v>
+      </c>
+      <c r="L8">
+        <v>0.03648868778280543</v>
+      </c>
+      <c r="M8">
+        <v>4.075</v>
+      </c>
+      <c r="N8">
+        <v>0.002903869450580774</v>
+      </c>
+      <c r="O8">
+        <v>0.0404265873015873</v>
+      </c>
+      <c r="P8">
+        <v>0.095</v>
+      </c>
+      <c r="Q8">
+        <v>6.769757001353952E-05</v>
+      </c>
+      <c r="R8">
+        <v>0.0009424603174603175</v>
+      </c>
+      <c r="S8">
+        <v>3.98</v>
+      </c>
+      <c r="T8">
+        <v>0.9766871165644171</v>
+      </c>
+      <c r="U8">
+        <v>6897.8</v>
+      </c>
+      <c r="V8">
+        <v>4.915413667783083</v>
+      </c>
+      <c r="W8">
+        <v>0.03933044597916423</v>
+      </c>
+      <c r="X8">
+        <v>0.1978713373455861</v>
+      </c>
+      <c r="Y8">
+        <v>-0.1585408913664219</v>
+      </c>
+      <c r="Z8">
+        <v>0.3355032244744289</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0.06748015502897491</v>
+      </c>
+      <c r="AC8">
+        <v>-0.06748015502897491</v>
+      </c>
+      <c r="AD8">
+        <v>10447.8</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>10447.8</v>
+      </c>
+      <c r="AG8">
+        <v>3549.999999999999</v>
+      </c>
+      <c r="AH8">
+        <v>0.8815890508054105</v>
+      </c>
+      <c r="AI8">
+        <v>0.6533019015401161</v>
+      </c>
+      <c r="AJ8">
+        <v>0.7166939212242343</v>
+      </c>
+      <c r="AK8">
+        <v>0.3903458134037054</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>National Bank of Kuwait S.A.K.P. (KWSE:NBK)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>0.0897</v>
+      </c>
+      <c r="E9">
+        <v>0.0793</v>
+      </c>
+      <c r="F9">
+        <v>0.0334</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>1915.6</v>
+      </c>
+      <c r="L9">
+        <v>0.5053686848700699</v>
+      </c>
+      <c r="M9">
+        <v>978.7</v>
+      </c>
+      <c r="N9">
+        <v>0.04043496403531604</v>
+      </c>
+      <c r="O9">
+        <v>0.5109104197118397</v>
+      </c>
+      <c r="P9">
+        <v>978.7</v>
+      </c>
+      <c r="Q9">
+        <v>0.04043496403531604</v>
+      </c>
+      <c r="R9">
+        <v>0.5109104197118397</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>14196.5</v>
+      </c>
+      <c r="V9">
+        <v>0.5865280136174151</v>
+      </c>
+      <c r="W9">
+        <v>0.1413351434305277</v>
+      </c>
+      <c r="X9">
+        <v>0.08109004955302002</v>
+      </c>
+      <c r="Y9">
+        <v>0.06024509387750765</v>
+      </c>
+      <c r="Z9">
+        <v>0.2147214936753318</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0.06798737550651285</v>
+      </c>
+      <c r="AC9">
+        <v>-0.06798737550651285</v>
+      </c>
+      <c r="AD9">
+        <v>19951.3</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>19951.3</v>
+      </c>
+      <c r="AG9">
+        <v>5754.799999999999</v>
+      </c>
+      <c r="AH9">
+        <v>0.4518407631195137</v>
+      </c>
+      <c r="AI9">
+        <v>0.5489632287390352</v>
+      </c>
+      <c r="AJ9">
+        <v>0.1920885473862699</v>
+      </c>
+      <c r="AK9">
+        <v>0.2598444040077482</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Commercial Bank of Kuwait K.P.S.C. (KWSE:CBK)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>0.0675</v>
+      </c>
+      <c r="E10">
+        <v>0.0907</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>328.3</v>
+      </c>
+      <c r="L10">
+        <v>0.6165258215962441</v>
+      </c>
+      <c r="M10">
+        <v>292.4</v>
+      </c>
+      <c r="N10">
+        <v>0.07790892861900828</v>
+      </c>
+      <c r="O10">
+        <v>0.8906487968321656</v>
+      </c>
+      <c r="P10">
+        <v>216.6</v>
+      </c>
+      <c r="Q10">
+        <v>0.05771229117263062</v>
+      </c>
+      <c r="R10">
+        <v>0.6597624124276575</v>
+      </c>
+      <c r="S10">
+        <v>75.79999999999998</v>
+      </c>
+      <c r="T10">
+        <v>0.2592339261285909</v>
+      </c>
+      <c r="U10">
+        <v>1710.7</v>
+      </c>
+      <c r="V10">
+        <v>0.4558098638458874</v>
+      </c>
+      <c r="W10">
+        <v>0.1522444815433129</v>
+      </c>
+      <c r="X10">
+        <v>0.08506910637919275</v>
+      </c>
+      <c r="Y10">
+        <v>0.06717537516412019</v>
+      </c>
+      <c r="Z10">
+        <v>0.1388020018767595</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0.06970284305861275</v>
+      </c>
+      <c r="AC10">
+        <v>-0.06970284305861275</v>
+      </c>
+      <c r="AD10">
+        <v>3940.3</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>3940.3</v>
+      </c>
+      <c r="AG10">
+        <v>2229.6</v>
+      </c>
+      <c r="AH10">
+        <v>0.5121662723893208</v>
+      </c>
+      <c r="AI10">
+        <v>0.641022303925556</v>
+      </c>
+      <c r="AJ10">
+        <v>0.3726745449379043</v>
+      </c>
+      <c r="AK10">
+        <v>0.5025923087326991</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>Burgan Bank K.P.S.C. (KWSE:BURG)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D5">
+      <c r="D11">
         <v>0.00417</v>
       </c>
-      <c r="E5">
+      <c r="E11">
         <v>-0.0999</v>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
         <v>152.5</v>
       </c>
-      <c r="L5">
+      <c r="L11">
         <v>0.2355212355212355</v>
       </c>
-      <c r="M5">
+      <c r="M11">
         <v>105.4</v>
       </c>
-      <c r="N5">
+      <c r="N11">
         <v>0.05100164521436176</v>
       </c>
-      <c r="O5">
+      <c r="O11">
         <v>0.6911475409836066</v>
       </c>
-      <c r="P5">
+      <c r="P11">
         <v>105.4</v>
       </c>
-      <c r="Q5">
+      <c r="Q11">
         <v>0.05100164521436176</v>
       </c>
-      <c r="R5">
+      <c r="R11">
         <v>0.6911475409836066</v>
       </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
         <v>1997.4</v>
       </c>
-      <c r="V5">
+      <c r="V11">
         <v>0.9665150488725444</v>
       </c>
-      <c r="W5">
+      <c r="W11">
         <v>0.05147331825699531</v>
       </c>
-      <c r="X5">
-        <v>0.1061004311629046</v>
-      </c>
-      <c r="Y5">
-        <v>-0.05462711290590932</v>
-      </c>
-      <c r="Z5">
+      <c r="X11">
+        <v>0.1060738080530842</v>
+      </c>
+      <c r="Y11">
+        <v>-0.05460048979608891</v>
+      </c>
+      <c r="Z11">
         <v>0.1116013719643565</v>
       </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0.06999142935518124</v>
-      </c>
-      <c r="AC5">
-        <v>-0.06999142935518124</v>
-      </c>
-      <c r="AD5">
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0.0699832142059786</v>
+      </c>
+      <c r="AC11">
+        <v>-0.0699832142059786</v>
+      </c>
+      <c r="AD11">
         <v>4630.7</v>
       </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
         <v>4630.7</v>
       </c>
-      <c r="AG5">
+      <c r="AG11">
         <v>2633.3</v>
       </c>
-      <c r="AH5">
+      <c r="AH11">
         <v>0.6914278888507309</v>
       </c>
-      <c r="AI5">
+      <c r="AI11">
         <v>0.5832189322283656</v>
       </c>
-      <c r="AJ5">
+      <c r="AJ11">
         <v>0.5602885167769527</v>
       </c>
-      <c r="AK5">
+      <c r="AK11">
         <v>0.4431299957930164</v>
       </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Al Ahli Bank of Kuwait K.S.C.P. (KWSE:ABK)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>0.0901</v>
+      </c>
+      <c r="E12">
+        <v>0.11</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>167.8</v>
+      </c>
+      <c r="L12">
+        <v>0.3229407236335643</v>
+      </c>
+      <c r="M12">
+        <v>69.3</v>
+      </c>
+      <c r="N12">
+        <v>0.03316741648320091</v>
+      </c>
+      <c r="O12">
+        <v>0.4129916567342073</v>
+      </c>
+      <c r="P12">
+        <v>69.3</v>
+      </c>
+      <c r="Q12">
+        <v>0.03316741648320091</v>
+      </c>
+      <c r="R12">
+        <v>0.4129916567342073</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>927.7</v>
+      </c>
+      <c r="V12">
+        <v>0.4440030630803101</v>
+      </c>
+      <c r="W12">
+        <v>0.08603804542890837</v>
+      </c>
+      <c r="X12">
+        <v>0.1169579424140945</v>
+      </c>
+      <c r="Y12">
+        <v>-0.03091989698518612</v>
+      </c>
+      <c r="Z12">
+        <v>0.07859033502230961</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0.07110975741376668</v>
+      </c>
+      <c r="AC12">
+        <v>-0.07110975741376668</v>
+      </c>
+      <c r="AD12">
+        <v>5971.1</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>5971.1</v>
+      </c>
+      <c r="AG12">
+        <v>5043.400000000001</v>
+      </c>
+      <c r="AH12">
+        <v>0.7407853110849203</v>
+      </c>
+      <c r="AI12">
+        <v>0.7219756967535216</v>
+      </c>
+      <c r="AJ12">
+        <v>0.7070715567519067</v>
+      </c>
+      <c r="AK12">
+        <v>0.6868497031105301</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
         <v>0</v>
       </c>
     </row>
